--- a/DATA/1.National Accounts_Data.xlsx
+++ b/DATA/1.National Accounts_Data.xlsx
@@ -1,11 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24228"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{694FBD1A-6E0C-40B9-91E0-342E3CE0742A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="795" windowWidth="14760" windowHeight="15405" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3510" yWindow="795" windowWidth="14760" windowHeight="15405"/>
   </bookViews>
   <sheets>
     <sheet name="GEO" sheetId="5" r:id="rId1"/>
@@ -230,7 +229,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="3">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
@@ -283,12 +282,18 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="12">
@@ -430,7 +435,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
@@ -499,11 +504,15 @@
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Style 1 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
+    <cellStyle name="Style 1 2" xfId="2"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -780,7 +789,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:I419"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -9550,10 +9559,10 @@
       <c r="D406" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="E406" t="s">
+      <c r="E406" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="F406" s="28">
+      <c r="F406" s="41">
         <v>98035.263407162434</v>
       </c>
       <c r="G406" s="2" t="s">
@@ -9637,10 +9646,10 @@
       <c r="D410" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="E410" t="s">
+      <c r="E410" s="40" t="s">
         <v>66</v>
       </c>
-      <c r="F410" s="28">
+      <c r="F410" s="41">
         <v>107780.82881385353</v>
       </c>
       <c r="G410" s="2" t="s">
@@ -9703,10 +9712,10 @@
       <c r="D413" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E413" t="s">
+      <c r="E413" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="F413" s="28">
+      <c r="F413" s="41">
         <v>19355.226256026603</v>
       </c>
       <c r="G413" s="2" t="s">
@@ -9830,10 +9839,10 @@
       <c r="D419" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="E419" s="4" t="s">
+      <c r="E419" s="42" t="s">
         <v>28</v>
       </c>
-      <c r="F419" s="30">
+      <c r="F419" s="43">
         <v>-2835.8834782014455</v>
       </c>
       <c r="G419" s="9" t="s">
@@ -9851,7 +9860,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:I419"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
